--- a/data/trans_orig/IP2903-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>26394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41904</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34243</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65736</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87410</t>
+          <t>87140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48309</t>
+          <t>47788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>55274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78564</t>
+          <t>77215</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100736</t>
+          <t>99694</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>63902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88374</t>
+          <t>89247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63844</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88533</t>
+          <t>88153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136210</t>
+          <t>136706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169068</t>
+          <t>169828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50888</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72237</t>
+          <t>73452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70268</t>
+          <t>71914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138041</t>
+          <t>138190</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95920</t>
+          <t>98075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122163</t>
+          <t>123211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101137</t>
+          <t>100391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127175</t>
+          <t>125841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203868</t>
+          <t>205951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239890</t>
+          <t>241401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>37556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55649</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60963</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84587</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108842</t>
+          <t>109569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>44419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64619</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65828</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44019</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61884</t>
+          <t>61070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97128</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122489</t>
+          <t>122623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46967</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68009</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67992</t>
+          <t>67654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98932</t>
+          <t>99211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128799</t>
+          <t>128084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>45986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37434</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57230</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>72155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97552</t>
+          <t>97193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84024</t>
+          <t>83335</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106136</t>
+          <t>106484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>87111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>110437</t>
+          <t>110319</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176347</t>
+          <t>176155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207431</t>
+          <t>209136</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194118</t>
+          <t>192578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232729</t>
+          <t>231965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207014</t>
+          <t>205974</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244556</t>
+          <t>246058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413238</t>
+          <t>412482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466694</t>
+          <t>467301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>151356</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>146354</t>
+          <t>149018</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181472</t>
+          <t>183634</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>272867</t>
+          <t>273024</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322976</t>
+          <t>323325</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>289042</t>
+          <t>288312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>330723</t>
+          <t>328554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>285120</t>
+          <t>285452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>327311</t>
+          <t>326420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586863</t>
+          <t>585398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>644251</t>
+          <t>646879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49195</t>
+          <t>47873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67857</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57371</t>
+          <t>57467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91152</t>
+          <t>91755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119557</t>
+          <t>118879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45350</t>
+          <t>46002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66573</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>53412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>73176</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45559</t>
+          <t>44770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>63951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103426</t>
+          <t>104600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131101</t>
+          <t>131161</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75518</t>
+          <t>76336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91704</t>
+          <t>91389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120195</t>
+          <t>118070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173450</t>
+          <t>174347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209887</t>
+          <t>212918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32787</t>
+          <t>33944</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39605</t>
+          <t>39424</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60255</t>
+          <t>59627</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78967</t>
+          <t>78098</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106812</t>
+          <t>107591</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>92254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117985</t>
+          <t>116989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97714</t>
+          <t>96948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123074</t>
+          <t>124343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196980</t>
+          <t>198365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234843</t>
+          <t>233409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49127</t>
+          <t>48801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49135</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>68676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103933</t>
+          <t>104888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131905</t>
+          <t>133564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46167</t>
+          <t>46768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>50306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73222</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>64632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>84400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49789</t>
+          <t>49844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70625</t>
+          <t>70279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118775</t>
+          <t>120404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148492</t>
+          <t>148894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>46052</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64703</t>
+          <t>66911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56085</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76873</t>
+          <t>76672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108342</t>
+          <t>106496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136496</t>
+          <t>135349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25875</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42757</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58384</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82712</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64617</t>
+          <t>65207</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85142</t>
+          <t>85951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66264</t>
+          <t>66647</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88159</t>
+          <t>88215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137263</t>
+          <t>137628</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>166326</t>
+          <t>167313</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240259</t>
+          <t>239779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281544</t>
+          <t>280987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256083</t>
+          <t>255816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298709</t>
+          <t>299894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507907</t>
+          <t>506417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>566039</t>
+          <t>568078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>137504</t>
+          <t>138761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136464</t>
+          <t>137938</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173196</t>
+          <t>171904</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>251068</t>
+          <t>250916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>298973</t>
+          <t>300625</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>297192</t>
+          <t>294882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338627</t>
+          <t>338753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280659</t>
+          <t>279708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>324636</t>
+          <t>323832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586847</t>
+          <t>588357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>648379</t>
+          <t>650487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30259</t>
+          <t>30176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46062</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72293</t>
+          <t>72917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44168</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58249</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>80800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>73404</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97452</t>
+          <t>97309</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121479</t>
+          <t>122534</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43157</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62100</t>
+          <t>62194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76393</t>
+          <t>76515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>103458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132681</t>
+          <t>132599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>54076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74922</t>
+          <t>75642</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>56068</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79003</t>
+          <t>78707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118040</t>
+          <t>115963</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>148631</t>
+          <t>147854</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80744</t>
+          <t>81112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102236</t>
+          <t>102957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111625</t>
+          <t>111168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138381</t>
+          <t>137132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198768</t>
+          <t>200234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233059</t>
+          <t>233566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>47449</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>68407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>53592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86889</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116424</t>
+          <t>116530</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>49468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70034</t>
+          <t>70563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56825</t>
+          <t>56121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91302</t>
+          <t>91628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120587</t>
+          <t>120715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60772</t>
+          <t>60958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82890</t>
+          <t>82607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83633</t>
+          <t>84199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>106803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149542</t>
+          <t>151245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182819</t>
+          <t>182455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>50035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70203</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44424</t>
+          <t>44269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64231</t>
+          <t>65313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101114</t>
+          <t>100296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129463</t>
+          <t>129234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62820</t>
+          <t>62811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78153</t>
+          <t>77605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104924</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57155</t>
+          <t>56740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79162</t>
+          <t>78372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49625</t>
+          <t>49855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>71245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112695</t>
+          <t>112423</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142556</t>
+          <t>142177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174185</t>
+          <t>175191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213377</t>
+          <t>213686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181207</t>
+          <t>180200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219387</t>
+          <t>220090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366362</t>
+          <t>367262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422108</t>
+          <t>422653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>180502</t>
+          <t>179875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>219455</t>
+          <t>218700</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>180249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216724</t>
+          <t>218865</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>368828</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>426157</t>
+          <t>425607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>275301</t>
+          <t>273762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>315692</t>
+          <t>317065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>304196</t>
+          <t>303314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>347574</t>
+          <t>346567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>590268</t>
+          <t>589484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>652471</t>
+          <t>650447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2903-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41770</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34371</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51088</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>34033</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41612</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26773</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>41775</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41770</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33796</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50056</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64964</t>
+          <t>65670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87140</t>
+          <t>86632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24241</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18418</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32206</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14598</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10005</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21670</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9486</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20199</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>15,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24241</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18021</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31482</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>29850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47788</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41600</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33418</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49385</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>38,66%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>45,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47702</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>39757</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55274</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>39992</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>55245</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>49,52%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>57,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>41600</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>33810</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50197</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77215</t>
+          <t>77557</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>100926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>107611</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>107611</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>107611</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>96332</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>96332</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>96332</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>107611</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>107611</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>107611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77081</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66361</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89687</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>75970</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63902</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89247</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63943</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>86445</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>77081</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>65013</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>88153</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136706</t>
+          <t>137048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169828</t>
+          <t>169439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -1291,74 +1291,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>60004</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49747</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>71818</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28,7%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>61736</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>51357</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>73452</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>51849</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>73448</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>29,59%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>60004</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50016</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>71914</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,98%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>28,74%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>183</t>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107431</t>
+          <t>107106</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138190</t>
+          <t>138194</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>113156</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>99890</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>125956</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>110486</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98075</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>123211</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>97985</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>123038</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>113156</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>100391</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>125841</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205951</t>
+          <t>206653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241401</t>
+          <t>241648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>372</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>248192</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>248192</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>248192</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50687</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>60508</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30,96%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>44,25%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45923</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37556</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55370</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>37316</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>54727</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>37,26%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,47%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>50687</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>42087</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>60545</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>84727</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109569</t>
+          <t>110018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33511</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26140</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42446</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20919</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14777</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28470</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14435</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27811</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33511</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26242</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>42394</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44419</t>
+          <t>44784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65579</t>
+          <t>64980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52536</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43398</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62148</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>56398</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47505</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65228</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>47584</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>65156</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>45,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>52536</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>43736</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>61070</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>96702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122623</t>
+          <t>121255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>123241</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>123241</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>123241</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,107 +2090,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56483</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47304</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68430</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>57274</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>47091</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>67438</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>48327</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>68750</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>36,48%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>113757</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>97389</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>127543</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>24,99%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>56483</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47079</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>67654</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>33,61%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>113757</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>99211</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>128084</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46841</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38746</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>56846</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>28148</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45986</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>27951</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>44655</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46841</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37754</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>56731</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72155</t>
+          <t>71050</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97193</t>
+          <t>96922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>97961</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>85952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>108820</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>48,67%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>94670</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>83335</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>106484</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>83427</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>105315</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>50,24%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>56,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>97961</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>87111</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>110319</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>48,67%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176155</t>
+          <t>177269</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209136</t>
+          <t>208662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>201285</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>201285</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>201285</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>201285</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>201285</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>201285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,107 +2546,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>226021</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>207445</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>248588</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>35,72%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>213200</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>192578</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>231965</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>193917</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>234849</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>32,49%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>226021</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>205974</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>246058</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>439222</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>413412</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>467735</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>32,48%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>439222</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>412482</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>467301</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>164597</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>146003</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>182241</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>133750</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>118225</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>150886</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>117719</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>151000</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>20,38%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>164597</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>149018</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>183634</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>273024</t>
+          <t>276086</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>323325</t>
+          <t>324587</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>305253</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>283044</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>324302</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43,87%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>309256</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>288312</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>328554</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>289545</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>331134</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>47,13%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>305253</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>285452</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>326420</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>585398</t>
+          <t>586359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>646879</t>
+          <t>641183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>695871</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>695871</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>695871</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>982</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>656206</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>656206</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>656206</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>695871</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>695871</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>695871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47646</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38897</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56553</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>57722</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66743</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48385</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66858</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47646</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38783</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>57467</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91755</t>
+          <t>91218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118879</t>
+          <t>118194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36151</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>45436</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18625</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12921</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25124</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26373</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36151</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28094</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46002</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66663</t>
+          <t>67127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>44633</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,28%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>62210</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53412</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73176</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>52390</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>72423</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>44,9%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>38,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>52,81%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>54462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>44770</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>63951</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>103420</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131161</t>
+          <t>130252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>138259</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>138259</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>138259</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>138557</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>138557</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>138557</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>138259</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>138259</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>138259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104659</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92648</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87049</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>76336</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99316</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>75031</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>99644</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>37,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>104659</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>91389</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>118070</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174347</t>
+          <t>173565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212918</t>
+          <t>209300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49296</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40046</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60578</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22,87%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42803</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>33944</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>52756</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>33215</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>53764</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>18,21%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>14,44%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49296</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>39424</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>59627</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78098</t>
+          <t>78403</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107591</t>
+          <t>106622</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110957</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98446</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>124636</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>105141</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92254</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116989</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>92663</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>118896</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110957</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>96948</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>124343</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,88%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198365</t>
+          <t>198333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233409</t>
+          <t>232273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59108</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>48952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>38,16%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>59090</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>48801</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>69748</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>49139</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>70463</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>37,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>59108</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>48594</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>68676</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>38,16%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>105268</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133564</t>
+          <t>133745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36442</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28333</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45155</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>23814</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16784</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32454</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16899</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36442</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>28770</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59334</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49684</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>70229</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74139</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>64632</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>84400</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>64347</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>84613</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>47,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>59334</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>49844</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>70279</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120404</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148894</t>
+          <t>148855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -4490,52 +4490,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,107 +4602,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>66121</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>56039</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>76104</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>55848</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46052</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66911</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45926</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>65980</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>33,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>66121</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55808</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76672</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>121969</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>108581</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>31,6%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>121969</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>106496</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>135349</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>30,99%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33528</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25213</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42649</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35982</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27523</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45296</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>27907</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>45498</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>21,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>33528</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25594</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>42502</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>58626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82329</t>
+          <t>82551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>76938</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>66671</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88832</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>43,57%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>50,31%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>75183</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>65207</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>85951</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>64566</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>85411</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>45,02%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>76938</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>66647</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>88215</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137628</t>
+          <t>137308</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167313</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>167013</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>167013</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>167013</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>277534</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>256798</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>301394</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>41,03%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>259708</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>239779</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>280987</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>240508</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>281654</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>37,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>277534</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>255816</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>299894</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506417</t>
+          <t>504958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568078</t>
+          <t>566354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>155416</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>138390</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>173718</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>21,16%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>18,84%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>121224</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>105783</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>138761</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>105901</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>141081</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>155416</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>137938</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>171904</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>250916</t>
+          <t>252306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>300625</t>
+          <t>301264</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>301690</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>280353</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>323791</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>41,07%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>38,16%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>44,07%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>316674</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>294882</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>338753</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>291129</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>336944</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>45,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>301690</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>279708</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>323832</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>588357</t>
+          <t>588712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>650487</t>
+          <t>651701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>734641</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>734641</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>734641</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>697606</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>697606</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>697606</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>734641</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>734641</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>734641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37706</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30209</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47038</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23571</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16781</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30176</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17020</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30455</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>37706</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29547</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46128</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50802</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72917</t>
+          <t>73722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33130</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41353</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36144</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28207</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43869</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28659</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44765</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33130</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25817</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42520</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>81662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>45813</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37708</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54482</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,33%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>64383</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56191</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73404</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>55093</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>72329</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>51,88%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>45,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>59,15%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>45813</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37646</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>54969</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97309</t>
+          <t>97977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>122032</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>116650</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116650</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>116650</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>124098</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>124098</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>124098</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>116650</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>116650</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>116650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55576</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76891</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52282</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43113</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62194</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>42143</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>62387</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>25,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>65031</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>54324</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76515</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103458</t>
+          <t>101474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132599</t>
+          <t>130619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67254</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>55958</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>79268</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26,27%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>30,96%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>64738</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>54076</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>75642</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>55217</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>76130</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>31,02%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>25,91%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67254</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>56068</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>78707</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>26,27%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>115963</t>
+          <t>117740</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147854</t>
+          <t>148922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>123751</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110847</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136285</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>91657</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81112</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102957</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>79790</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>103559</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>123751</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>111168</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>137132</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200234</t>
+          <t>197898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233566</t>
+          <t>234034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>256036</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>256036</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>256036</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>208678</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>208678</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>208678</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>256036</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>256036</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>256036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42828</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34240</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52259</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>57743</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>47449</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>68407</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>47170</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>68674</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,67%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>42828</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33535</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53592</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87421</t>
+          <t>86178</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116530</t>
+          <t>113930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46115</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36762</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56407</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>58957</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49468</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>70563</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>47388</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>68864</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46115</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36218</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56121</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91628</t>
+          <t>91395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120715</t>
+          <t>121996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>95413</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83324</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>105551</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>71582</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60958</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>82607</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>61164</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>83468</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>95413</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84199</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>106803</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151245</t>
+          <t>150507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182455</t>
+          <t>182893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188282</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188282</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188282</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54985</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44952</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66269</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>59982</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50035</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72335</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>48629</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>70242</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54985</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>44269</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>65313</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100296</t>
+          <t>101372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129234</t>
+          <t>129281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51710</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42211</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>61886</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>39219</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29971</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>49887</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>30624</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>49131</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>51710</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42344</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>62811</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77605</t>
+          <t>76997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>105124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59657</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>50019</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70609</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>35,86%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>30,07%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>42,45%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>67803</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>56740</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>78372</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>58347</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>78653</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>40,6%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>46,93%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>59657</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>49855</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>71245</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>35,86%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112423</t>
+          <t>114402</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142177</t>
+          <t>144574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>166352</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>166352</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>166352</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>167003</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>167003</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>167003</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>166352</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>166352</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>166352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>200551</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>183860</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>222075</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>193578</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>175191</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>213686</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>174876</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>214060</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>28,13%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>200551</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>180200</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>220090</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367262</t>
+          <t>367324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422653</t>
+          <t>422925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>198209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>179218</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>216562</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>199058</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>179875</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>218700</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>180567</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>219236</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,93%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>198209</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>180249</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>218865</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>366803</t>
+          <t>369875</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>425607</t>
+          <t>421711</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>324634</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>304775</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>346943</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47,96%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>295425</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>273762</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>317065</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>272825</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>317407</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>42,94%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>324634</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>303314</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>346567</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589484</t>
+          <t>589142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>650447</t>
+          <t>650971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>688060</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>688060</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>688060</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
